--- a/artfynd/A 59493-2025 artfynd.xlsx
+++ b/artfynd/A 59493-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136206180</v>
       </c>
       <c r="B2" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136206175</v>
       </c>
       <c r="B3" t="n">
-        <v>96520</v>
+        <v>96521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136206169</v>
       </c>
       <c r="B4" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136206190</v>
       </c>
       <c r="B5" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136206196</v>
       </c>
       <c r="B6" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136206182</v>
       </c>
       <c r="B7" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>136206170</v>
       </c>
       <c r="B8" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136206177</v>
       </c>
       <c r="B9" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136206183</v>
       </c>
       <c r="B10" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136206172</v>
       </c>
       <c r="B11" t="n">
-        <v>58844</v>
+        <v>58845</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136206197</v>
       </c>
       <c r="B12" t="n">
-        <v>56903</v>
+        <v>56904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 59493-2025 artfynd.xlsx
+++ b/artfynd/A 59493-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136206180</v>
       </c>
       <c r="B2" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136206175</v>
       </c>
       <c r="B3" t="n">
-        <v>96521</v>
+        <v>96527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136206169</v>
       </c>
       <c r="B4" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136206190</v>
       </c>
       <c r="B5" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136206196</v>
       </c>
       <c r="B6" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136206182</v>
       </c>
       <c r="B7" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>136206170</v>
       </c>
       <c r="B8" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136206177</v>
       </c>
       <c r="B9" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136206183</v>
       </c>
       <c r="B10" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136206172</v>
       </c>
       <c r="B11" t="n">
-        <v>58845</v>
+        <v>58849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136206197</v>
       </c>
       <c r="B12" t="n">
-        <v>56904</v>
+        <v>56908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 59493-2025 artfynd.xlsx
+++ b/artfynd/A 59493-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136206180</v>
       </c>
       <c r="B2" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136206175</v>
       </c>
       <c r="B3" t="n">
-        <v>96527</v>
+        <v>96528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136206169</v>
       </c>
       <c r="B4" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136206190</v>
       </c>
       <c r="B5" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136206196</v>
       </c>
       <c r="B6" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136206182</v>
       </c>
       <c r="B7" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>136206170</v>
       </c>
       <c r="B8" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136206177</v>
       </c>
       <c r="B9" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136206183</v>
       </c>
       <c r="B10" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136206172</v>
       </c>
       <c r="B11" t="n">
-        <v>58849</v>
+        <v>58850</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136206197</v>
       </c>
       <c r="B12" t="n">
-        <v>56908</v>
+        <v>56909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 59493-2025 artfynd.xlsx
+++ b/artfynd/A 59493-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136206180</v>
       </c>
       <c r="B2" t="n">
-        <v>96888</v>
+        <v>96899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136206175</v>
       </c>
       <c r="B3" t="n">
-        <v>96528</v>
+        <v>96539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59493-2025 artfynd.xlsx
+++ b/artfynd/A 59493-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136206180</v>
       </c>
       <c r="B2" t="n">
-        <v>96899</v>
+        <v>96912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136206175</v>
       </c>
       <c r="B3" t="n">
-        <v>96539</v>
+        <v>96552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136206169</v>
       </c>
       <c r="B4" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136206190</v>
       </c>
       <c r="B5" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136206196</v>
       </c>
       <c r="B6" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136206182</v>
       </c>
       <c r="B7" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>136206170</v>
       </c>
       <c r="B8" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136206177</v>
       </c>
       <c r="B9" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136206183</v>
       </c>
       <c r="B10" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136206172</v>
       </c>
       <c r="B11" t="n">
-        <v>58850</v>
+        <v>58855</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136206197</v>
       </c>
       <c r="B12" t="n">
-        <v>56909</v>
+        <v>56914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 59493-2025 artfynd.xlsx
+++ b/artfynd/A 59493-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136206180</v>
       </c>
       <c r="B2" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136206175</v>
       </c>
       <c r="B3" t="n">
-        <v>96552</v>
+        <v>96553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59493-2025 artfynd.xlsx
+++ b/artfynd/A 59493-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136206180</v>
       </c>
       <c r="B2" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136206175</v>
       </c>
       <c r="B3" t="n">
-        <v>96553</v>
+        <v>96566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136206169</v>
       </c>
       <c r="B4" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136206190</v>
       </c>
       <c r="B5" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136206196</v>
       </c>
       <c r="B6" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136206182</v>
       </c>
       <c r="B7" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>136206170</v>
       </c>
       <c r="B8" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136206177</v>
       </c>
       <c r="B9" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136206183</v>
       </c>
       <c r="B10" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136206172</v>
       </c>
       <c r="B11" t="n">
-        <v>58855</v>
+        <v>58868</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136206197</v>
       </c>
       <c r="B12" t="n">
-        <v>56914</v>
+        <v>56927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 59493-2025 artfynd.xlsx
+++ b/artfynd/A 59493-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136206180</v>
       </c>
       <c r="B2" t="n">
-        <v>96926</v>
+        <v>96927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136206175</v>
       </c>
       <c r="B3" t="n">
-        <v>96566</v>
+        <v>96567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
